--- a/Team-Data/2013-14/12-29-2013-14.xlsx
+++ b/Team-Data/2013-14/12-29-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,22 +728,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.548</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>48.8</v>
       </c>
       <c r="I2" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
         <v>83.3</v>
@@ -685,34 +752,34 @@
         <v>0.468</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="N2" t="n">
         <v>0.383</v>
       </c>
       <c r="O2" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P2" t="n">
         <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T2" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U2" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="V2" t="n">
         <v>15.2</v>
@@ -724,46 +791,46 @@
         <v>4.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>6</v>
@@ -772,13 +839,13 @@
         <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -799,19 +866,19 @@
         <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -963,7 +1030,7 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
         <v>18</v>
@@ -981,13 +1048,13 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1130,10 +1197,10 @@
         <v>16</v>
       </c>
       <c r="AM4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>5</v>
@@ -1142,10 +1209,10 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>22</v>
@@ -1157,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
@@ -1303,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
@@ -1509,10 +1576,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -1571,52 +1638,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="H7" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="I7" t="n">
         <v>36.8</v>
       </c>
       <c r="J7" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.363</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
         <v>21.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R7" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
         <v>43.5</v>
@@ -1631,25 +1698,25 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z7" t="n">
         <v>19.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC7" t="n">
         <v>-5.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1661,25 +1728,25 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
         <v>21</v>
@@ -1691,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>17</v>
@@ -1709,16 +1776,16 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AY7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1864,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1873,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
         <v>22</v>
@@ -1885,7 +1952,7 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1897,10 +1964,10 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-1</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
@@ -2034,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
@@ -2043,13 +2110,13 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2073,7 +2140,7 @@
         <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
@@ -2085,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>19</v>
@@ -2213,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>13</v>
@@ -2264,7 +2331,7 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.594</v>
+        <v>0.581</v>
       </c>
       <c r="H11" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J11" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L11" t="n">
         <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0.727</v>
@@ -2344,13 +2411,13 @@
         <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="T11" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
         <v>17.2</v>
@@ -2359,25 +2426,25 @@
         <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC11" t="n">
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,31 +2456,31 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
         <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -2434,7 +2501,7 @@
         <v>29</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -2443,16 +2510,16 @@
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.636</v>
+        <v>0.656</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.477</v>
       </c>
       <c r="L12" t="n">
         <v>9.199999999999999</v>
@@ -2511,67 +2578,67 @@
         <v>26.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="P12" t="n">
         <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.696</v>
+        <v>0.701</v>
       </c>
       <c r="R12" t="n">
         <v>10.8</v>
       </c>
       <c r="S12" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="U12" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA12" t="n">
         <v>24.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.7</v>
+        <v>106.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2589,10 +2656,10 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2607,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2625,16 +2692,16 @@
         <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
@@ -2765,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
@@ -2783,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2950,7 +3017,7 @@
         <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
         <v>26</v>
@@ -2965,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
         <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2980,10 +3047,10 @@
         <v>5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -3027,64 +3094,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.419</v>
+        <v>0.433</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="L15" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O15" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="P15" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
       <c r="R15" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>42.7</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X15" t="n">
         <v>5.9</v>
@@ -3096,85 +3163,85 @@
         <v>20.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>12</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>16</v>
@@ -3299,16 +3366,16 @@
         <v>18</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>26</v>
@@ -3329,7 +3396,7 @@
         <v>18</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
         <v>24</v>
@@ -3356,7 +3423,7 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>20</v>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3678,13 +3745,13 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
@@ -3693,7 +3760,7 @@
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
@@ -3854,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>12</v>
@@ -3863,10 +3930,10 @@
         <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3881,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3908,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
@@ -4036,10 +4103,10 @@
         <v>4</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM20" t="n">
         <v>27</v>
@@ -4051,7 +4118,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF21" t="n">
         <v>27</v>
@@ -4209,7 +4276,7 @@
         <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>25</v>
@@ -4227,16 +4294,16 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
@@ -4263,10 +4330,10 @@
         <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.833</v>
+        <v>0.828</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="J22" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.471</v>
+        <v>0.467</v>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S22" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="T22" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="U22" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
         <v>8</v>
@@ -4367,19 +4434,19 @@
         <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.1</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,37 +4458,37 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM22" t="n">
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4448,10 +4515,10 @@
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4483,154 +4550,154 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.449</v>
+        <v>0.446</v>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M23" t="n">
         <v>20.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O23" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z23" t="n">
         <v>20.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>20.5</v>
-      </c>
       <c r="AA23" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>97.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM23" t="n">
         <v>16</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ23" t="n">
         <v>19</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>6</v>
       </c>
       <c r="AT23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV23" t="n">
         <v>19</v>
       </c>
-      <c r="AU23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>20</v>
-      </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3</v>
+        <v>0.276</v>
       </c>
       <c r="H24" t="n">
         <v>49.2</v>
@@ -4683,46 +4750,46 @@
         <v>39.5</v>
       </c>
       <c r="J24" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="K24" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M24" t="n">
         <v>22.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="P24" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.715</v>
+        <v>0.71</v>
       </c>
       <c r="R24" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S24" t="n">
         <v>33.2</v>
       </c>
       <c r="T24" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U24" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V24" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="W24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X24" t="n">
         <v>4.2</v>
@@ -4731,28 +4798,28 @@
         <v>6.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
         <v>19.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>102.7</v>
+        <v>102.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.9</v>
+        <v>-9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AF24" t="n">
         <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
@@ -4764,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>15</v>
@@ -4776,22 +4843,22 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT24" t="n">
         <v>7</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4800,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>26</v>
@@ -4809,7 +4876,7 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>6</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
@@ -4997,7 +5064,7 @@
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>6</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5134,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
         <v>1</v>
@@ -5143,7 +5210,7 @@
         <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5155,7 +5222,7 @@
         <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
         <v>4</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
         <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.31</v>
+        <v>0.321</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J27" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K27" t="n">
         <v>0.443</v>
@@ -5238,94 +5305,94 @@
         <v>6.9</v>
       </c>
       <c r="M27" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
       <c r="O27" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T27" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U27" t="n">
         <v>20.6</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
         <v>5.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>9</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ27" t="n">
         <v>8</v>
@@ -5334,10 +5401,10 @@
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU27" t="n">
         <v>20</v>
@@ -5352,16 +5419,16 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA27" t="n">
         <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -5393,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.774</v>
+        <v>0.767</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J28" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.395</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="P28" t="n">
         <v>18.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.762</v>
       </c>
       <c r="R28" t="n">
         <v>9.300000000000001</v>
@@ -5441,16 +5508,16 @@
         <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U28" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V28" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
         <v>4.5</v>
@@ -5465,16 +5532,16 @@
         <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC28" t="n">
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
         <v>4</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,13 +5571,13 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5525,13 +5592,13 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>0.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
         <v>16</v>
@@ -5671,7 +5738,7 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5683,13 +5750,13 @@
         <v>12</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
@@ -5698,7 +5765,7 @@
         <v>6</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT29" t="n">
         <v>15</v>
@@ -5707,13 +5774,13 @@
         <v>28</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF30" t="n">
         <v>29</v>
@@ -5868,10 +5935,10 @@
         <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ30" t="n">
         <v>14</v>
@@ -5889,7 +5956,7 @@
         <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>22</v>
@@ -5904,7 +5971,7 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6090,22 @@
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI31" t="n">
         <v>14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
         <v>9</v>
@@ -6053,19 +6120,19 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6074,10 +6141,10 @@
         <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-29-2013-14</t>
+          <t>2013-12-29</t>
         </is>
       </c>
     </row>
